--- a/stories/arbres/TREE-VIV-007.xlsx
+++ b/stories/arbres/TREE-VIV-007.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nino est au jardin avec papa. Une poule picore. Papa dit : on prend soin avec un adulte. On est doux. Nino porte le petit seau avec papa. Ils versent un peu d'eau, tout doux.</t>
+          <t>Nino est au jardin avec papa. Une poule picore. On prend soin avec un adulte. On est doux. Nino porte le petit seau avec papa. Ils versent un peu d'eau, tout doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nino est au jardin avec papa. Une poule picore.
+papa|On prend soin avec un adulte. On est doux.
+narrateur|Nino porte le petit seau avec papa. Ils versent un peu d'eau, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le grillage, l'abreuvoir, ou le bac.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Près du grillage, Nino verse avec papa. Avec un adulte. Il est doux. La poule boit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Près du grillage, comment Nino aide-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a pris soin avec un adulte. Il a été doux.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la poule, le chat, ou le lapin.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nino verse l'eau pour la poule. Papa, l'adulte, tient le seau. Nino est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2581,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2748,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné l'eau à la poule, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2915,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3082,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné les graines à la poule, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3249,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3416,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné le foin à la poule, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3583,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3750,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat miaule. Nino pose le bol, tout doux. Avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3941,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4108,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné l'eau à le chat, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4275,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4442,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné les graines à le chat, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4609,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4776,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné le foin à le chat, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4943,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5110,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Le lapin attend. Nino approche le foin, doux. Papa, l'adulte, est près.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5301,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5468,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné l'eau à le lapin, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5635,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5802,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné les graines à le lapin, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5969,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6136,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné le foin à le lapin, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6303,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6470,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|À l'abreuvoir, Nino pose le seau, tout doux. Papa, l'adulte, guide. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|À l'abreuvoir, comment Nino aide-t-il ?</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6833,6 +7017,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la poule, le chat, ou le lapin.</t>
         </is>
       </c>
     </row>
@@ -6997,6 +7186,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|À l'abreuvoir, la poule boit. Nino est doux. Avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7183,6 +7377,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7345,6 +7544,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné l'eau à la poule, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7507,6 +7711,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7669,6 +7878,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné les graines à la poule, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7831,6 +8045,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7993,6 +8212,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné le foin à la poule, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8155,6 +8379,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8317,6 +8546,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat s'approche. Nino verse, tout doux. Papa, l'adulte, sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8503,6 +8737,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8665,6 +8904,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné l'eau à le chat, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8827,6 +9071,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8989,6 +9238,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné les graines à le chat, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9151,6 +9405,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9313,6 +9572,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné le foin à le chat, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9475,6 +9739,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9637,6 +9906,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Le lapin trempe le nez. Nino reste doux. Avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9823,6 +10097,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9985,6 +10264,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné l'eau à le lapin, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10147,6 +10431,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10309,6 +10598,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné les graines à le lapin, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10471,6 +10765,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10633,6 +10932,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné le foin à le lapin, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10795,6 +11099,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10957,6 +11266,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, Nino et papa, l'adulte, mettent l'eau. Nino reste doux. La poule s'approche.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11133,6 +11447,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, comment Nino aide-t-il ?</t>
         </is>
       </c>
     </row>
@@ -11301,6 +11620,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a versé l'eau avec papa. Tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11489,6 +11813,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la poule, le chat, ou le lapin.</t>
         </is>
       </c>
     </row>
@@ -11653,6 +11982,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, la poule picore. Nino verse, doux. Avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11839,6 +12173,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12001,6 +12340,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné l'eau à la poule, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12163,6 +12507,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12325,6 +12674,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné les graines à la poule, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12487,6 +12841,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12649,6 +13008,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné le foin à la poule, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12811,6 +13175,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12973,6 +13342,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat du bac. Nino pose l'eau, tout doux. Papa, l'adulte, aide.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13159,6 +13533,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13321,6 +13700,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné l'eau à le chat, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13483,6 +13867,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13645,6 +14034,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné les graines à le chat, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13807,6 +14201,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13969,6 +14368,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné le foin à le chat, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14131,6 +14535,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14293,6 +14702,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Le lapin du bac. Nino est doux. Avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14479,6 +14893,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14641,6 +15060,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné l'eau à le lapin, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14803,6 +15227,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14965,6 +15394,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné les graines à le lapin, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15127,6 +15561,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15289,6 +15728,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a donné le foin à le lapin, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15451,6 +15895,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15469,7 +15918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15493,6 +15942,13 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-VIV-007.xlsx
+++ b/stories/arbres/TREE-VIV-007.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Nino porte le petit seau avec papa. Ils versent un peu d'eau, tout doux.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le grillage, l'abreuvoir, ou le bac.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
           <t>narrateur|Près du grillage, Nino verse avec papa. Avec un adulte. Il est doux. La poule boit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|Près du grillage, comment Nino aide-t-il ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Nino a pris soin avec un adulte. Il a été doux.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2228,6 +2238,7 @@
           <t>narrateur|On peut prendre la poule, le chat, ou le lapin.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2406,7 @@
           <t>narrateur|Nino verse l'eau pour la poule. Papa, l'adulte, tient le seau. Nino est doux.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2586,6 +2598,7 @@
           <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2753,6 +2766,7 @@
           <t>narrateur|Nino a donné l'eau à la poule, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2920,6 +2934,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3087,6 +3102,7 @@
           <t>narrateur|Nino a donné les graines à la poule, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3254,6 +3270,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3421,6 +3438,7 @@
           <t>narrateur|Nino a donné le foin à la poule, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3588,6 +3606,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3755,6 +3774,7 @@
           <t>narrateur|Le chat miaule. Nino pose le bol, tout doux. Avec un adulte.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3946,6 +3966,7 @@
           <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4113,6 +4134,7 @@
           <t>narrateur|Nino a donné l'eau à le chat, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4280,6 +4302,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4447,6 +4470,7 @@
           <t>narrateur|Nino a donné les graines à le chat, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4614,6 +4638,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4781,6 +4806,7 @@
           <t>narrateur|Nino a donné le foin à le chat, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4948,6 +4974,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5115,6 +5142,7 @@
           <t>narrateur|Le lapin attend. Nino approche le foin, doux. Papa, l'adulte, est près.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5306,6 +5334,7 @@
           <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5473,6 +5502,7 @@
           <t>narrateur|Nino a donné l'eau à le lapin, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5640,6 +5670,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5807,6 +5838,7 @@
           <t>narrateur|Nino a donné les graines à le lapin, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5974,6 +6006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6141,6 +6174,7 @@
           <t>narrateur|Nino a donné le foin à le lapin, près de le grillage. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6308,6 +6342,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
           <t>narrateur|À l'abreuvoir, Nino pose le seau, tout doux. Papa, l'adulte, guide. On est doux.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|À l'abreuvoir, comment Nino aide-t-il ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6866,7 @@
           <t>narrateur|Oui. Avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7024,6 +7062,7 @@
           <t>narrateur|On peut prendre la poule, le chat, ou le lapin.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7191,6 +7230,7 @@
           <t>narrateur|À l'abreuvoir, la poule boit. Nino est doux. Avec un adulte.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7382,6 +7422,7 @@
           <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7549,6 +7590,7 @@
           <t>narrateur|Nino a donné l'eau à la poule, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7716,6 +7758,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7883,6 +7926,7 @@
           <t>narrateur|Nino a donné les graines à la poule, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8050,6 +8094,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8217,6 +8262,7 @@
           <t>narrateur|Nino a donné le foin à la poule, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8384,6 +8430,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8551,6 +8598,7 @@
           <t>narrateur|Le chat s'approche. Nino verse, tout doux. Papa, l'adulte, sourit.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8742,6 +8790,7 @@
           <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8909,6 +8958,7 @@
           <t>narrateur|Nino a donné l'eau à le chat, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9076,6 +9126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9243,6 +9294,7 @@
           <t>narrateur|Nino a donné les graines à le chat, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9410,6 +9462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9577,6 +9630,7 @@
           <t>narrateur|Nino a donné le foin à le chat, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9744,6 +9798,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9911,6 +9966,7 @@
           <t>narrateur|Le lapin trempe le nez. Nino reste doux. Avec un adulte.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10102,6 +10158,7 @@
           <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10269,6 +10326,7 @@
           <t>narrateur|Nino a donné l'eau à le lapin, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10436,6 +10494,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10603,6 +10662,7 @@
           <t>narrateur|Nino a donné les graines à le lapin, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10770,6 +10830,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10937,6 +10998,7 @@
           <t>narrateur|Nino a donné le foin à le lapin, près de l'abreuvoir. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11104,6 +11166,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11271,6 +11334,7 @@
           <t>narrateur|Au bac, Nino et papa, l'adulte, mettent l'eau. Nino reste doux. La poule s'approche.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11454,6 +11518,7 @@
           <t>narrateur|Au bac, comment Nino aide-t-il ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11625,6 +11690,7 @@
           <t>narrateur|Nino a versé l'eau avec papa. Tout doux.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11820,6 +11886,7 @@
           <t>narrateur|On peut prendre la poule, le chat, ou le lapin.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11987,6 +12054,7 @@
           <t>narrateur|Au bac, la poule picore. Nino verse, doux. Avec un adulte.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12178,6 +12246,7 @@
           <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12345,6 +12414,7 @@
           <t>narrateur|Nino a donné l'eau à la poule, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12512,6 +12582,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12679,6 +12750,7 @@
           <t>narrateur|Nino a donné les graines à la poule, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12846,6 +12918,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13013,6 +13086,7 @@
           <t>narrateur|Nino a donné le foin à la poule, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13180,6 +13254,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13347,6 +13422,7 @@
           <t>narrateur|Le chat du bac. Nino pose l'eau, tout doux. Papa, l'adulte, aide.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13538,6 +13614,7 @@
           <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13705,6 +13782,7 @@
           <t>narrateur|Nino a donné l'eau à le chat, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13872,6 +13950,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14039,6 +14118,7 @@
           <t>narrateur|Nino a donné les graines à le chat, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14206,6 +14286,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14373,6 +14454,7 @@
           <t>narrateur|Nino a donné le foin à le chat, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14540,6 +14622,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14707,6 +14790,7 @@
           <t>narrateur|Le lapin du bac. Nino est doux. Avec un adulte.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14898,6 +14982,7 @@
           <t>narrateur|On peut prendre l'eau, les graines, ou le foin.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15065,6 +15150,7 @@
           <t>narrateur|Nino a donné l'eau à le lapin, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15232,6 +15318,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15399,6 +15486,7 @@
           <t>narrateur|Nino a donné les graines à le lapin, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15566,6 +15654,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15733,6 +15822,7 @@
           <t>narrateur|Nino a donné le foin à le lapin, près de le bac. Avec un adulte. Il a été doux. Papa range le seau.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15900,6 +15990,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15918,7 +16009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15949,6 +16040,20 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15963,7 +16068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16150,6 +16255,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
